--- a/artfynd/A 3636-2025 artfynd.xlsx
+++ b/artfynd/A 3636-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121999326</v>
+        <v>121999327</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>359910</v>
+        <v>359882</v>
       </c>
       <c r="R2" t="n">
-        <v>6423734</v>
+        <v>6423739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121999325</v>
+        <v>121999326</v>
       </c>
       <c r="B3" t="n">
         <v>8425</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>359918</v>
+        <v>359910</v>
       </c>
       <c r="R3" t="n">
-        <v>6423741</v>
+        <v>6423734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121999327</v>
+        <v>121999325</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>359882</v>
+        <v>359918</v>
       </c>
       <c r="R4" t="n">
-        <v>6423739</v>
+        <v>6423741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 3636-2025 artfynd.xlsx
+++ b/artfynd/A 3636-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121999327</v>
+        <v>121999326</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>359882</v>
+        <v>359910</v>
       </c>
       <c r="R2" t="n">
-        <v>6423739</v>
+        <v>6423734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121999326</v>
+        <v>121999327</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>359910</v>
+        <v>359882</v>
       </c>
       <c r="R3" t="n">
-        <v>6423734</v>
+        <v>6423739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3636-2025 artfynd.xlsx
+++ b/artfynd/A 3636-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121999326</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121999327</v>
+        <v>121999325</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>359882</v>
+        <v>359918</v>
       </c>
       <c r="R3" t="n">
-        <v>6423739</v>
+        <v>6423741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121999325</v>
+        <v>121999327</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>359918</v>
+        <v>359882</v>
       </c>
       <c r="R4" t="n">
-        <v>6423741</v>
+        <v>6423739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 3636-2025 artfynd.xlsx
+++ b/artfynd/A 3636-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121999326</v>
+        <v>121999325</v>
       </c>
       <c r="B2" t="n">
         <v>8430</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>359910</v>
+        <v>359918</v>
       </c>
       <c r="R2" t="n">
-        <v>6423734</v>
+        <v>6423741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121999325</v>
+        <v>121999327</v>
       </c>
       <c r="B3" t="n">
-        <v>8430</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>359918</v>
+        <v>359882</v>
       </c>
       <c r="R3" t="n">
-        <v>6423741</v>
+        <v>6423739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121999327</v>
+        <v>121999326</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>359882</v>
+        <v>359910</v>
       </c>
       <c r="R4" t="n">
-        <v>6423739</v>
+        <v>6423734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
